--- a/tests/fixtures/21_monthly_budget/21_monthly_budget_pattern-from-claude.xlsx
+++ b/tests/fixtures/21_monthly_budget/21_monthly_budget_pattern-from-claude.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>instr_title</t>
+          <t>instr_income_proj</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Title of this worksheet is in cell at right. Next instruction is in cell A4.</t>
+          <t>Projected Monthly Income label is in cell at right. Enter Income 1 in cell E4 and Extra Income in E5 to calculate Total monthly income in E6. Next instruction is in cell A6.</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -581,7 +581,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>instr_income_proj</t>
+          <t>header_proj_income</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -591,7 +591,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Projected Monthly Income label is in cell at right. Enter Income 1 in cell E4 and Extra Income in E5 to calculate Total monthly income in E6. Next instruction is in cell A6.</t>
+          <t>PROJECTED MONTHLY INCOME</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>header_proj_income</t>
+          <t>header_income_1_proj</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>PROJECTED MONTHLY INCOME</t>
+          <t>Income 1</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
@@ -639,7 +639,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>header_income_1_proj</t>
+          <t>header_income_amount_proj</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Income 1</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
@@ -668,7 +668,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>header_income_amount_proj</t>
+          <t>header_proj_balance</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>PROJECTED BALANCE (Projected income minus expenses)</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -697,7 +697,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>header_proj_balance</t>
+          <t>header_balance_amount_proj</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>PROJECTED BALANCE (Projected income minus expenses)</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="E9" s="2" t="n"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>header_balance_amount_proj</t>
+          <t>instr_income_actual</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>Actual Monthly Income label is in cell at right. Enter Income 1 in cell E8 and Extra Income in E9 to calculate Total monthly income in E10. Next instruction is in cell A12.</t>
         </is>
       </c>
       <c r="E10" s="2" t="n"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>instr_income_actual</t>
+          <t>header_actual_income</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Actual Monthly Income label is in cell at right. Enter Income 1 in cell E8 and Extra Income in E9 to calculate Total monthly income in E10. Next instruction is in cell A12.</t>
+          <t>ACTUAL MONTHLY INCOME</t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
@@ -784,7 +784,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>header_actual_income</t>
+          <t>header_income_1_actual</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>ACTUAL MONTHLY INCOME</t>
+          <t>Income 1</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -813,7 +813,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>header_income_1_actual</t>
+          <t>header_income_amount_actual</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Income 1</t>
+          <t>4000</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>header_income_amount_actual</t>
+          <t>header_diff</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4000</t>
+          <t>DIFFERENCE (Actual minus projected)</t>
         </is>
       </c>
       <c r="E14" s="2" t="n"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>header_diff</t>
+          <t>header_diff_amount</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>DIFFERENCE (Actual minus projected)</t>
+          <t>-341</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -900,7 +900,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>header_diff_amount</t>
+          <t>instr_expenses</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -910,7 +910,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-341</t>
+          <t>Enter details in Housing table starting in cell at right and in Entertainment table starting in cell G12. Next instruction is in cell A25.</t>
         </is>
       </c>
       <c r="E16" s="2" t="n"/>
@@ -929,7 +929,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>instr_expenses</t>
+          <t>header_housing</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Enter details in Housing table starting in cell at right and in Entertainment table starting in cell G12. Next instruction is in cell A25.</t>
+          <t>HOUSING</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
@@ -958,7 +958,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>header_housing</t>
+          <t>header_housing_proj_cost</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>HOUSING</t>
+          <t>Projected Cost</t>
         </is>
       </c>
       <c r="E18" s="2" t="n"/>
@@ -987,7 +987,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>header_housing_proj_cost</t>
+          <t>header_housing_actual_cost</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Projected Cost</t>
+          <t>Actual Cost</t>
         </is>
       </c>
       <c r="E19" s="2" t="n"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>header_housing_actual_cost</t>
+          <t>header_housing_diff</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Actual Cost</t>
+          <t>Difference</t>
         </is>
       </c>
       <c r="E20" s="2" t="n"/>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>header_housing_diff</t>
+          <t>header_entertainment</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Difference</t>
+          <t>ENTERTAINMENT</t>
         </is>
       </c>
       <c r="E21" s="2" t="n"/>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>header_entertainment</t>
+          <t>header_entertainment_proj_cost</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>ENTERTAINMENT</t>
+          <t>Projected Cost</t>
         </is>
       </c>
       <c r="E22" s="2" t="n"/>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>header_entertainment_proj_cost</t>
+          <t>header_entertainment_actual_cost</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Projected Cost</t>
+          <t>Actual Cost</t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>header_entertainment_actual_cost</t>
+          <t>header_entertainment_diff</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Actual Cost</t>
+          <t>Difference</t>
         </is>
       </c>
       <c r="E24" s="2" t="n"/>
@@ -1154,33 +1154,33 @@
       <c r="K24" s="2" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>lbl:</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>header_entertainment_diff</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n"/>
-      <c r="F25" s="2" t="n"/>
-      <c r="G25" s="2" t="n"/>
-      <c r="H25" s="2" t="n"/>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="2" t="n"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>var:</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>income_proj.description</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>.*</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n"/>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
+      <c r="J25" s="3" t="n"/>
+      <c r="K25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1190,17 +1190,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>budget.title</t>
+          <t>income_proj.amount</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>PERSONAL MONTHLY BUDGET</t>
+          <t>-?\d+(\.\d{2})?</t>
         </is>
       </c>
       <c r="E26" s="3" t="n"/>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>income_proj.description</t>
+          <t>balance_proj.description</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>income_proj.amount</t>
+          <t>balance_proj.amount</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>balance_proj.description</t>
+          <t>income_actual.description</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>balance_proj.amount</t>
+          <t>income_actual.amount</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>income_actual.description</t>
+          <t>expense.instruction</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>income_actual.amount</t>
+          <t>housing.description</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>-?\d+(\.\d{2})?</t>
+          <t>.*</t>
         </is>
       </c>
       <c r="E32" s="3" t="n"/>
@@ -1393,17 +1393,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>expense.instruction</t>
+          <t>housing.projected_cost</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>-?\d+(\.\d{2})?</t>
         </is>
       </c>
       <c r="E33" s="3" t="n"/>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>housing.description</t>
+          <t>housing.actual_cost</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>-?\d+(\.\d{2})?</t>
         </is>
       </c>
       <c r="E34" s="3" t="n"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>housing.projected_cost</t>
+          <t>housing.difference</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -1480,17 +1480,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>housing.actual_cost</t>
+          <t>entertainment.description</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>-?\d+(\.\d{2})?</t>
+          <t>.*</t>
         </is>
       </c>
       <c r="E36" s="3" t="n"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>housing.difference</t>
+          <t>entertainment.projected_cost</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>entertainment.description</t>
+          <t>entertainment.actual_cost</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>-?\d+(\.\d{2})?</t>
         </is>
       </c>
       <c r="E38" s="3" t="n"/>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>entertainment.projected_cost</t>
+          <t>entertainment.difference</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -1589,501 +1589,401 @@
       <c r="K39" s="3" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>START:</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>instr_intro</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>cell:next</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="n"/>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>instr_income_proj</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>header_proj_income</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>header_income_1_proj</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>header_income_amount_proj</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>header_proj_balance</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>header_balance_amount_proj</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="n"/>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>DATA:2</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>income_proj.description</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>income_proj.amount</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>balance_proj.description</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>balance_proj.amount</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="n"/>
+      <c r="J45" s="3" t="n"/>
+      <c r="K45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="6" t="n"/>
+      <c r="I46" s="6" t="n"/>
+      <c r="J46" s="6" t="n"/>
+      <c r="K46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>instr_income_actual</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>header_actual_income</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>header_income_1_actual</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>header_income_amount_actual</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>header_diff</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>header_diff_amount</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n"/>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="n"/>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>DATA:2</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>income_actual.description</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>income_actual.amount</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>IGNORE</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>table:*</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="n"/>
+      <c r="I49" s="6" t="n"/>
+      <c r="J49" s="6" t="n"/>
+      <c r="K49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>HEADER:1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>instr_expenses</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>header_housing</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>header_housing_proj_cost</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>header_housing_actual_cost</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>header_housing_diff</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>header_entertainment</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>header_entertainment_proj_cost</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>header_entertainment_actual_cost</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>header_entertainment_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n"/>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>DATA:{0,52}</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>expense.instruction</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>housing.description</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>housing.projected_cost</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>housing.actual_cost</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>housing.difference</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>entertainment.description</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>entertainment.projected_cost</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>entertainment.actual_cost</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>-?\d+(\.\d{2})?</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="n"/>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
-      <c r="I40" s="3" t="n"/>
-      <c r="J40" s="3" t="n"/>
-      <c r="K40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>var:</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
         <is>
           <t>entertainment.difference</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>-?\d+(\.\d{2})?</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n"/>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>START:</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>instr_intro</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="n"/>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
-      <c r="H43" s="5" t="n"/>
-      <c r="I43" s="5" t="n"/>
-      <c r="J43" s="5" t="n"/>
-      <c r="K43" s="5" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n"/>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
-      <c r="H44" s="5" t="n"/>
-      <c r="I44" s="5" t="n"/>
-      <c r="J44" s="5" t="n"/>
-      <c r="K44" s="5" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>instr_title</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="n"/>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
-      <c r="H45" s="5" t="n"/>
-      <c r="I45" s="5" t="n"/>
-      <c r="J45" s="5" t="n"/>
-      <c r="K45" s="5" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>cell:next</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>budget.title</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="n"/>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
-      <c r="H46" s="5" t="n"/>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="5" t="n"/>
-      <c r="K46" s="5" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>table:*</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="6" t="n"/>
-      <c r="H47" s="6" t="n"/>
-      <c r="I47" s="6" t="n"/>
-      <c r="J47" s="6" t="n"/>
-      <c r="K47" s="6" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>instr_income_proj</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>header_proj_income</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>header_income_1_proj</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>header_income_amount_proj</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>header_proj_balance</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>header_balance_amount_proj</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="2" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="n"/>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>DATA:2</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>income_proj.description</t>
-        </is>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>income_proj.amount</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t>balance_proj.description</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t>balance_proj.amount</t>
-        </is>
-      </c>
-      <c r="I49" s="3" t="n"/>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="3" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>table:*</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="6" t="n"/>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
-      <c r="I50" s="6" t="n"/>
-      <c r="J50" s="6" t="n"/>
-      <c r="K50" s="6" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="n"/>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>instr_income_actual</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>header_actual_income</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>header_income_1_actual</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>header_income_amount_actual</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>header_diff</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>header_diff_amount</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="n"/>
-      <c r="J51" s="2" t="n"/>
-      <c r="K51" s="2" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n"/>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>DATA:2</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>income_actual.description</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="inlineStr">
-        <is>
-          <t>income_actual.amount</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t>IGNORE</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="n"/>
-      <c r="J52" s="3" t="n"/>
-      <c r="K52" s="3" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>table:*</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="n"/>
-      <c r="C53" s="6" t="n"/>
-      <c r="D53" s="6" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="6" t="n"/>
-      <c r="G53" s="6" t="n"/>
-      <c r="H53" s="6" t="n"/>
-      <c r="I53" s="6" t="n"/>
-      <c r="J53" s="6" t="n"/>
-      <c r="K53" s="6" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n"/>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>HEADER:1</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>instr_expenses</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>header_housing</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>header_housing_proj_cost</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>header_housing_actual_cost</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>header_housing_diff</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>header_entertainment</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>header_entertainment_proj_cost</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>header_entertainment_actual_cost</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>header_entertainment_diff</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="n"/>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>DATA:{0,52}</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>expense.instruction</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>housing.description</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>housing.projected_cost</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>housing.actual_cost</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>housing.difference</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>entertainment.description</t>
-        </is>
-      </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>entertainment.projected_cost</t>
-        </is>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>entertainment.actual_cost</t>
-        </is>
-      </c>
-      <c r="K55" s="3" t="inlineStr">
-        <is>
-          <t>entertainment.difference</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>END:</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
-      <c r="J56" s="4" t="n"/>
-      <c r="K56" s="4" t="n"/>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
